--- a/data/trans_orig/IP32-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP32-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22903</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88439</t>
+          <t>88772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98846</t>
+          <t>98881</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96704</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109015</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>188811</t>
+          <t>189313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205045</t>
+          <t>204766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37859</t>
+          <t>37839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19422</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>35727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>213895</t>
+          <t>213172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230329</t>
+          <t>230901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>91,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>227884</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>219069</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>234778</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>90,04%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>86,56%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>450414</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>439241</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>461037</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>86,86%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>91,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>227884</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>219829</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>234716</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>90,04%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>86,86%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>450414</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>437755</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>460676</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>89,07%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>86,56%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108530</t>
+          <t>109082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119341</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124528</t>
+          <t>124948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135098</t>
+          <t>135061</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236975</t>
+          <t>236650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252492</t>
+          <t>251937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21929</t>
+          <t>21667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>176456</t>
+          <t>176827</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>187676</t>
+          <t>187567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>175739</t>
+          <t>175582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>190163</t>
+          <t>190167</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356801</t>
+          <t>356906</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>374246</t>
+          <t>374745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23978</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>24984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>53586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78306</t>
+          <t>78284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23981</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41576</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>61271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>87207</t>
+          <t>87948</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>602637</t>
+          <t>601674</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>625959</t>
+          <t>626517</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>632968</t>
+          <t>632812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>659522</t>
+          <t>658334</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1242459</t>
+          <t>1243199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1278423</t>
+          <t>1278122</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>144135</t>
+          <t>143366</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142194</t>
+          <t>142198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>288026</t>
+          <t>288388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14761</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8716</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221050</t>
+          <t>219619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>231272</t>
+          <t>230810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>250164</t>
+          <t>251154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>263085</t>
+          <t>263191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>476124</t>
+          <t>475642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>492380</t>
+          <t>492066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139129</t>
+          <t>139923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150952</t>
+          <t>151003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139060</t>
+          <t>138875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151585</t>
+          <t>151817</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283060</t>
+          <t>282538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300895</t>
+          <t>300355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22937</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>34532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145573</t>
+          <t>144909</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>159925</t>
+          <t>159873</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156925</t>
+          <t>155713</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>170527</t>
+          <t>169950</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>306170</t>
+          <t>307366</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>326758</t>
+          <t>326720</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17557</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39897</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69352</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17406</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32504</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>661289</t>
+          <t>661036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>683636</t>
+          <t>682673</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>700794</t>
+          <t>701929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>723993</t>
+          <t>724527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1369732</t>
+          <t>1371707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1402025</t>
+          <t>1403888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126503</t>
+          <t>126556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131118</t>
+          <t>131123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117518</t>
+          <t>117887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123539</t>
+          <t>123552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>247130</t>
+          <t>246597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>254092</t>
+          <t>254097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202857</t>
+          <t>202293</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209296</t>
+          <t>209211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>246584</t>
+          <t>246767</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255331</t>
+          <t>255075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>453162</t>
+          <t>451905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>463146</t>
+          <t>463103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174109</t>
+          <t>173526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184025</t>
+          <t>183937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180929</t>
+          <t>180881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187859</t>
+          <t>187496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>358650</t>
+          <t>357908</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>370618</t>
+          <t>370092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26926</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11143</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>150639</t>
+          <t>150313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164473</t>
+          <t>164379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156179</t>
+          <t>155896</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>167806</t>
+          <t>167901</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>312404</t>
+          <t>311723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329756</t>
+          <t>329770</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>28032</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>665699</t>
+          <t>665910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>684384</t>
+          <t>683685</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>713216</t>
+          <t>713081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>730234</t>
+          <t>729719</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1384679</t>
+          <t>1384601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1411031</t>
+          <t>1409256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52051</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56993</t>
+          <t>56883</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60618</t>
+          <t>60560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113609</t>
+          <t>112949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118424</t>
+          <t>118288</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>11018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145419</t>
+          <t>145619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155541</t>
+          <t>155585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170057</t>
+          <t>169071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178992</t>
+          <t>179328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318781</t>
+          <t>319713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332475</t>
+          <t>333149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>15884</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>19919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>157002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171862</t>
+          <t>171715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200822</t>
+          <t>199743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210134</t>
+          <t>209892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361747</t>
+          <t>362435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380287</t>
+          <t>379728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>12510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>263162</t>
+          <t>263667</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>271549</t>
+          <t>271692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>269485</t>
+          <t>274238</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>299789</t>
+          <t>299867</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>539709</t>
+          <t>539959</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>569292</t>
+          <t>569216</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>42390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58996</t>
+          <t>54243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>629554</t>
+          <t>630853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>650883</t>
+          <t>650820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>715563</t>
+          <t>714587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>745770</t>
+          <t>745205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1354823</t>
+          <t>1357004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1391371</t>
+          <t>1391987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
